--- a/data/trans_orig/P15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44246</t>
+          <t>43361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73525</t>
+          <t>71979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62275</t>
+          <t>64713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96441</t>
+          <t>98925</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114353</t>
+          <t>115552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159281</t>
+          <t>161307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>958198</t>
+          <t>959744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>987477</t>
+          <t>988362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1218672</t>
+          <t>1216188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1252838</t>
+          <t>1250400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2187554</t>
+          <t>2185528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2232482</t>
+          <t>2231283</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122093</t>
+          <t>122076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168577</t>
+          <t>169265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57781</t>
+          <t>56050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92048</t>
+          <t>90909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190405</t>
+          <t>192117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248786</t>
+          <t>250188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1524836</t>
+          <t>1524148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1571320</t>
+          <t>1571337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1495625</t>
+          <t>1496764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1529892</t>
+          <t>1531623</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3032300</t>
+          <t>3030898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3090681</t>
+          <t>3088969</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56027</t>
+          <t>56100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>33224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>49962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81982</t>
+          <t>81194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495381</t>
+          <t>495308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521980</t>
+          <t>522006</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442259</t>
+          <t>443188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461716</t>
+          <t>461175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>945838</t>
+          <t>946626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>977346</t>
+          <t>977858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>213412</t>
+          <t>212290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>272920</t>
+          <t>275280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151081</t>
+          <t>151993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206321</t>
+          <t>204526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379017</t>
+          <t>381713</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>461354</t>
+          <t>466311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3003623</t>
+          <t>3001263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3063131</t>
+          <t>3064253</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3172876</t>
+          <t>3174671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3228116</t>
+          <t>3227204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6194387</t>
+          <t>6189430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6276724</t>
+          <t>6274028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62314</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97233</t>
+          <t>95860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93283</t>
+          <t>94564</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134098</t>
+          <t>135045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164501</t>
+          <t>165127</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217435</t>
+          <t>218708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>877410</t>
+          <t>878783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>912329</t>
+          <t>912704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1203699</t>
+          <t>1202752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1244514</t>
+          <t>1243233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2095005</t>
+          <t>2093732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2147939</t>
+          <t>2147313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159502</t>
+          <t>157846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215843</t>
+          <t>211690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95845</t>
+          <t>96659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137272</t>
+          <t>139530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>267418</t>
+          <t>264125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>333199</t>
+          <t>336039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1748114</t>
+          <t>1752267</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1804455</t>
+          <t>1806111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1620531</t>
+          <t>1618273</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1661958</t>
+          <t>1661144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3388561</t>
+          <t>3385721</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3454342</t>
+          <t>3457635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37462</t>
+          <t>38947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42585</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>41647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73152</t>
+          <t>72458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443719</t>
+          <t>442234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463207</t>
+          <t>463561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416046</t>
+          <t>416219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439885</t>
+          <t>439587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866661</t>
+          <t>867355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>897390</t>
+          <t>898166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>255706</t>
+          <t>257533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>320934</t>
+          <t>321909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227345</t>
+          <t>227761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288260</t>
+          <t>293375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>501766</t>
+          <t>502430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>591069</t>
+          <t>595514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3098848</t>
+          <t>3097873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3164076</t>
+          <t>3162249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3265970</t>
+          <t>3260855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3326885</t>
+          <t>3326469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6382943</t>
+          <t>6378498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6472246</t>
+          <t>6471582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>32769</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60203</t>
+          <t>58300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56915</t>
+          <t>58576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94899</t>
+          <t>94646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98435</t>
+          <t>99503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141593</t>
+          <t>143804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>694144</t>
+          <t>696047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>718828</t>
+          <t>721578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>899761</t>
+          <t>900014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>937745</t>
+          <t>936084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1607414</t>
+          <t>1605203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1650572</t>
+          <t>1649504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101789</t>
+          <t>101819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144417</t>
+          <t>144095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68335</t>
+          <t>69051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104860</t>
+          <t>105455</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>177975</t>
+          <t>181209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236559</t>
+          <t>236608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1931968</t>
+          <t>1932290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1974596</t>
+          <t>1974566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1883440</t>
+          <t>1882845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1919965</t>
+          <t>1919249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3828126</t>
+          <t>3828077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3886710</t>
+          <t>3883476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44211</t>
+          <t>42922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42838</t>
+          <t>44127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47486</t>
+          <t>46850</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79438</t>
+          <t>79024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502675</t>
+          <t>503964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525863</t>
+          <t>526444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>506302</t>
+          <t>505013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527941</t>
+          <t>528522</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016589</t>
+          <t>1017003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1048541</t>
+          <t>1049177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171078</t>
+          <t>171679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228763</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164248</t>
+          <t>163040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225432</t>
+          <t>221032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352827</t>
+          <t>351252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>432517</t>
+          <t>430988</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3148855</t>
+          <t>3151761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3206540</t>
+          <t>3205939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3306668</t>
+          <t>3311068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3367852</t>
+          <t>3369060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6477201</t>
+          <t>6478730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6556891</t>
+          <t>6558466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47577</t>
+          <t>48251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67066</t>
+          <t>68711</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93662</t>
+          <t>91824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99938</t>
+          <t>101759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131727</t>
+          <t>132273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467361</t>
+          <t>466687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488014</t>
+          <t>487957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661846</t>
+          <t>663684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>688442</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1138719</t>
+          <t>1138173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1170508</t>
+          <t>1168687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89279</t>
+          <t>89655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161290</t>
+          <t>161968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71960</t>
+          <t>74458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124239</t>
+          <t>126286</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188556</t>
+          <t>179662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>272139</t>
+          <t>275357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2129037</t>
+          <t>2128359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2201048</t>
+          <t>2200672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2113584</t>
+          <t>2111537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2165863</t>
+          <t>2163365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4256011</t>
+          <t>4252793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4339594</t>
+          <t>4348488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48930</t>
+          <t>49295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40291</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>50233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81609</t>
+          <t>86321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597693</t>
+          <t>597328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>624075</t>
+          <t>624103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>620172</t>
+          <t>619838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>637793</t>
+          <t>636851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225477</t>
+          <t>1220765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1256625</t>
+          <t>1256853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155673</t>
+          <t>154496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234796</t>
+          <t>233781</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173967</t>
+          <t>172036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245320</t>
+          <t>242475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357869</t>
+          <t>358589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>460265</t>
+          <t>466272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3217093</t>
+          <t>3218108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3296216</t>
+          <t>3297393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3408474</t>
+          <t>3411319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3479827</t>
+          <t>3481758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6645418</t>
+          <t>6639411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6747814</t>
+          <t>6747094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>42431</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71979</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64713</t>
+          <t>61590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98925</t>
+          <t>98660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115552</t>
+          <t>113670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161307</t>
+          <t>161200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>959744</t>
+          <t>960988</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>988362</t>
+          <t>989292</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1216188</t>
+          <t>1216453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1250400</t>
+          <t>1253523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2185528</t>
+          <t>2185635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2231283</t>
+          <t>2233165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122076</t>
+          <t>123470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169265</t>
+          <t>170235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56050</t>
+          <t>58432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>91216</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192117</t>
+          <t>192324</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250188</t>
+          <t>250070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1524148</t>
+          <t>1523178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1571337</t>
+          <t>1569943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1496764</t>
+          <t>1496457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1531623</t>
+          <t>1529241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3030898</t>
+          <t>3031016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3088969</t>
+          <t>3088762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29402</t>
+          <t>29876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56100</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33224</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49962</t>
+          <t>51019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81194</t>
+          <t>82053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495308</t>
+          <t>496468</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522006</t>
+          <t>521532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443188</t>
+          <t>441609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461175</t>
+          <t>460689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>946626</t>
+          <t>945767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>977858</t>
+          <t>976801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>212290</t>
+          <t>215378</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275280</t>
+          <t>275818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151993</t>
+          <t>151737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204526</t>
+          <t>203313</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>381713</t>
+          <t>376930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>466311</t>
+          <t>462125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3001263</t>
+          <t>3000725</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3064253</t>
+          <t>3061165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3174671</t>
+          <t>3175884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3227204</t>
+          <t>3227460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6189430</t>
+          <t>6193616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6274028</t>
+          <t>6278811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61939</t>
+          <t>61078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95860</t>
+          <t>97467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94564</t>
+          <t>94478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135045</t>
+          <t>132563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165127</t>
+          <t>164255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218708</t>
+          <t>216531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>878783</t>
+          <t>877176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>912704</t>
+          <t>913565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1202752</t>
+          <t>1205234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1243233</t>
+          <t>1243319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2093732</t>
+          <t>2095909</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2147313</t>
+          <t>2148185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>157846</t>
+          <t>162096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211690</t>
+          <t>210092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96659</t>
+          <t>96184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139530</t>
+          <t>136388</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>264125</t>
+          <t>267879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>336039</t>
+          <t>333060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1752267</t>
+          <t>1753865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1806111</t>
+          <t>1801861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1618273</t>
+          <t>1621415</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1661144</t>
+          <t>1661619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3385721</t>
+          <t>3388700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3457635</t>
+          <t>3453881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17620</t>
+          <t>17596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38947</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42412</t>
+          <t>40957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41647</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72458</t>
+          <t>72960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>442234</t>
+          <t>443691</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463561</t>
+          <t>463585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416219</t>
+          <t>417674</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439587</t>
+          <t>440603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867355</t>
+          <t>866853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>898166</t>
+          <t>898634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>257533</t>
+          <t>255281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321909</t>
+          <t>321982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227761</t>
+          <t>225783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>293375</t>
+          <t>287235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>502430</t>
+          <t>502918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>595514</t>
+          <t>592317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3097873</t>
+          <t>3097800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3162249</t>
+          <t>3164501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3260855</t>
+          <t>3266995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3326469</t>
+          <t>3328447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6378498</t>
+          <t>6381695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6471582</t>
+          <t>6471094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>35248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58300</t>
+          <t>59008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58576</t>
+          <t>58393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94646</t>
+          <t>95206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99503</t>
+          <t>98507</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143804</t>
+          <t>142802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>696047</t>
+          <t>695339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>721578</t>
+          <t>719099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>900014</t>
+          <t>899454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>936084</t>
+          <t>936267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1605203</t>
+          <t>1606205</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1649504</t>
+          <t>1650500</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101819</t>
+          <t>102243</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144095</t>
+          <t>142726</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69051</t>
+          <t>68347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105455</t>
+          <t>105413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181209</t>
+          <t>179468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236608</t>
+          <t>237422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1932290</t>
+          <t>1933659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1974566</t>
+          <t>1974142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1882845</t>
+          <t>1882887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1919249</t>
+          <t>1919953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3828077</t>
+          <t>3827263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3883476</t>
+          <t>3885217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42922</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>21047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44127</t>
+          <t>44236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46850</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79024</t>
+          <t>78747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503964</t>
+          <t>503422</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526444</t>
+          <t>525286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505013</t>
+          <t>504904</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>528522</t>
+          <t>528093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1017003</t>
+          <t>1017280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1049177</t>
+          <t>1049799</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171679</t>
+          <t>173136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225857</t>
+          <t>228107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163040</t>
+          <t>165114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>221032</t>
+          <t>223138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>351252</t>
+          <t>350062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430988</t>
+          <t>430630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3151761</t>
+          <t>3149511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3205939</t>
+          <t>3204482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3311068</t>
+          <t>3308962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3369060</t>
+          <t>3366986</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6478730</t>
+          <t>6479088</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6558466</t>
+          <t>6559656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48251</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>73024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91824</t>
+          <t>100620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101759</t>
+          <t>106146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132273</t>
+          <t>138909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>479332</t>
+          <t>540686</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466687</t>
+          <t>529316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487957</t>
+          <t>550224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>675954</t>
+          <t>737517</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663684</t>
+          <t>721418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>749014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1155286</t>
+          <t>1278203</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1138173</t>
+          <t>1261658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1168687</t>
+          <t>1294421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>140218</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89655</t>
+          <t>117711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161968</t>
+          <t>170901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74458</t>
+          <t>93502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126286</t>
+          <t>135064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>231999</t>
+          <t>251245</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179662</t>
+          <t>219912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275357</t>
+          <t>285099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2160285</t>
+          <t>2090348</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2128359</t>
+          <t>2059665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2200672</t>
+          <t>2112855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2135866</t>
+          <t>2060365</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2111537</t>
+          <t>2036328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2163365</t>
+          <t>2077890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4296151</t>
+          <t>4150714</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4252793</t>
+          <t>4116860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4348488</t>
+          <t>4182047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49295</t>
+          <t>61608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23612</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40625</t>
+          <t>45134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50233</t>
+          <t>60605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86321</t>
+          <t>98328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>613397</t>
+          <t>669918</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597328</t>
+          <t>649979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>624103</t>
+          <t>682349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>629597</t>
+          <t>699638</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619838</t>
+          <t>689743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>636851</t>
+          <t>709156</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1242994</t>
+          <t>1369556</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1220765</t>
+          <t>1348136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1256853</t>
+          <t>1385859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>198874</t>
+          <t>219729</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154496</t>
+          <t>188290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>233781</t>
+          <t>252663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172036</t>
+          <t>204535</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>242475</t>
+          <t>258138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>411252</t>
+          <t>450517</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>358589</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>466272</t>
+          <t>497354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3253015</t>
+          <t>3300954</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3218108</t>
+          <t>3268020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3297393</t>
+          <t>3332393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3441417</t>
+          <t>3497519</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3411319</t>
+          <t>3470169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3481758</t>
+          <t>3523772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6694431</t>
+          <t>6798473</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6639411</t>
+          <t>6751636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6747094</t>
+          <t>6836727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
